--- a/experiments/02_term_expansion_by_language_pair/report/dev_v1_proper_term_across_languages.xlsx
+++ b/experiments/02_term_expansion_by_language_pair/report/dev_v1_proper_term_across_languages.xlsx
@@ -572,28 +572,28 @@
   <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/02_term_expansion_by_language_pair/report/dev_v1_proper_term_across_languages.xlsx
+++ b/experiments/02_term_expansion_by_language_pair/report/dev_v1_proper_term_across_languages.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,14 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -39,38 +45,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFF8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,22 +176,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -828,14 +807,14 @@
       <c r="U3" s="6" t="n">
         <v>0.8042635658914731</v>
       </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="V3" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
+      <c r="A4" s="8" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Qwen 3B</t>
@@ -892,7 +871,7 @@
       <c r="Q4" s="6" t="n">
         <v>0.8888097183427748</v>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -906,7 +885,7 @@
       <c r="U4" s="6" t="n">
         <v>0.7635658914728684</v>
       </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="V4" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -984,7 +963,7 @@
       <c r="U5" s="6" t="n">
         <v>0.8023255813953492</v>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1001,13 +980,13 @@
           <t>GPT</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="7" t="n">
         <v>53.1453355808675</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="7" t="n">
         <v>43.14643446007593</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="7" t="n">
         <v>65.50039397469644</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1015,13 +994,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="7" t="n">
         <v>77.62256268271634</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="7" t="n">
         <v>72.49607633493659</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="7" t="n">
         <v>82.2376779517852</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1029,13 +1008,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="5" t="n">
         <v>74.98295841854123</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="5" t="n">
         <v>79.41860465116279</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="5" t="n">
         <v>93.16479400749064</v>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -1043,13 +1022,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="5" t="n">
         <v>0.9444055155334643</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.9410865653968022</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="5" t="n">
         <v>0.9592626054286718</v>
       </c>
       <c r="R6" s="7" t="inlineStr">
@@ -1057,13 +1036,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="S6" s="11" t="n">
+      <c r="S6" s="5" t="n">
         <v>0.8634772462077019</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" s="5" t="n">
         <v>0.7905491698595148</v>
       </c>
-      <c r="U6" s="11" t="n">
+      <c r="U6" s="5" t="n">
         <v>0.8735262593783482</v>
       </c>
       <c r="V6" s="7" t="inlineStr">
@@ -1073,19 +1052,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Qwen 3B</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="7" t="n">
         <v>35.35130261696263</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="7" t="n">
         <v>24.50251689199042</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="7" t="n">
         <v>53.02564888932073</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1093,13 +1072,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="7" t="n">
         <v>67.49950716527168</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="7" t="n">
         <v>51.43974204368619</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="7" t="n">
         <v>74.20603887944995</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1107,13 +1086,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="5" t="n">
         <v>67.41649625085208</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="L7" s="7" t="n">
         <v>63.25581395348837</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="7" t="n">
         <v>84.6441947565543</v>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -1121,13 +1100,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="5" t="n">
         <v>0.9328954887283994</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="5" t="n">
         <v>0.929367787712117</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="5" t="n">
         <v>0.952411616990798</v>
       </c>
       <c r="R7" s="7" t="inlineStr">
@@ -1135,13 +1114,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="S7" s="11" t="n">
+      <c r="S7" s="5" t="n">
         <v>0.8366394399066506</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" s="5" t="n">
         <v>0.7509578544061314</v>
       </c>
-      <c r="U7" s="11" t="n">
+      <c r="U7" s="5" t="n">
         <v>0.8510182207931405</v>
       </c>
       <c r="V7" s="7" t="inlineStr">
@@ -1157,13 +1136,13 @@
           <t>Qwen 7B</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="7" t="n">
         <v>40.7526662444401</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="7" t="n">
         <v>37.86997424719835</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="7" t="n">
         <v>60.71345945287555</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1171,13 +1150,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="7" t="n">
         <v>70.86410519427808</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="7" t="n">
         <v>66.91761393964684</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="7" t="n">
         <v>79.39122185435912</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1185,13 +1164,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="5" t="n">
         <v>70.3817314246762</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="5" t="n">
         <v>77.20930232558139</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="5" t="n">
         <v>91.19850187265918</v>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -1199,13 +1178,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="5" t="n">
         <v>0.9402285151418706</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="5" t="n">
         <v>0.9337816222779055</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="5" t="n">
         <v>0.9571928135673363</v>
       </c>
       <c r="R8" s="7" t="inlineStr">
@@ -1213,13 +1192,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="S8" s="11" t="n">
+      <c r="S8" s="5" t="n">
         <v>0.8553092182030346</v>
       </c>
-      <c r="T8" s="11" t="n">
+      <c r="T8" s="5" t="n">
         <v>0.7713920817369087</v>
       </c>
-      <c r="U8" s="11" t="n">
+      <c r="U8" s="5" t="n">
         <v>0.8703108252947471</v>
       </c>
       <c r="V8" s="7" t="inlineStr">
@@ -1239,13 +1218,13 @@
           <t>GPT</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="5" t="n">
         <v>51.2444459978333</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="5" t="n">
         <v>39.22004586297616</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="5" t="n">
         <v>61.13116300094295</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1253,13 +1232,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="5" t="n">
         <v>75.69544530598721</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="5" t="n">
         <v>68.37085045032345</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="5" t="n">
         <v>79.03354646336024</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -1267,13 +1246,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="7" t="n">
         <v>80.20833333333334</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="7" t="n">
         <v>79.60288808664259</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="7" t="n">
         <v>95.75070821529745</v>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -1281,49 +1260,49 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="7" t="n">
         <v>0.9788424541467304</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="P9" s="7" t="n">
         <v>0.967973963461328</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="7" t="n">
         <v>0.9724740321057601</v>
       </c>
-      <c r="R9" s="8" t="inlineStr">
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
-      <c r="S9" s="10" t="n">
+      <c r="S9" s="7" t="n">
         <v>0.9493087557603689</v>
       </c>
-      <c r="T9" s="10" t="n">
+      <c r="T9" s="7" t="n">
         <v>0.912121212121212</v>
       </c>
-      <c r="U9" s="10" t="n">
+      <c r="U9" s="7" t="n">
         <v>0.9215686274509802</v>
       </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="V9" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Qwen 3B</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="5" t="n">
         <v>32.31917493311038</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="5" t="n">
         <v>22.15069141606213</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="5" t="n">
         <v>47.58248173916545</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1331,13 +1310,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="5" t="n">
         <v>64.25464758424178</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="5" t="n">
         <v>48.66651896547258</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="5" t="n">
         <v>69.97206301318633</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -1345,13 +1324,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="7" t="n">
         <v>72.8125</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="5" t="n">
         <v>62.63537906137184</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="5" t="n">
         <v>84.13597733711048</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -1359,30 +1338,30 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="7" t="n">
         <v>0.9774800637958532</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="7" t="n">
         <v>0.9667432447215839</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="7" t="n">
         <v>0.9704640496425198</v>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
-      <c r="S10" s="10" t="n">
+      <c r="S10" s="7" t="n">
         <v>0.9447004608294933</v>
       </c>
-      <c r="T10" s="10" t="n">
+      <c r="T10" s="7" t="n">
         <v>0.9030303030303031</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="U10" s="7" t="n">
         <v>0.9150326797385622</v>
       </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="V10" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1395,13 +1374,13 @@
           <t>Qwen 7B</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="5" t="n">
         <v>36.2882873129007</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="5" t="n">
         <v>34.1533276636256</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="5" t="n">
         <v>56.11348123756358</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1409,13 +1388,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="5" t="n">
         <v>67.48956991652733</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="5" t="n">
         <v>62.69327996652142</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="5" t="n">
         <v>76.02376874031519</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1423,13 +1402,13 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="7" t="n">
         <v>72.34375</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="7" t="n">
         <v>77.97833935018051</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="7" t="n">
         <v>92.06798866855524</v>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -1437,30 +1416,30 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="O11" s="7" t="n">
         <v>0.974571620813397</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="P11" s="7" t="n">
         <v>0.9691773328957446</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="7" t="n">
         <v>0.9720018885741264</v>
       </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="R11" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
       </c>
-      <c r="S11" s="10" t="n">
+      <c r="S11" s="7" t="n">
         <v>0.9400921658986178</v>
       </c>
-      <c r="T11" s="10" t="n">
+      <c r="T11" s="7" t="n">
         <v>0.9121212121212121</v>
       </c>
-      <c r="U11" s="10" t="n">
+      <c r="U11" s="7" t="n">
         <v>0.9215686274509802</v>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="V11" s="7" t="inlineStr">
         <is>
           <t>ende</t>
         </is>

--- a/experiments/02_term_expansion_by_language_pair/report/dev_v1_proper_term_across_languages.xlsx
+++ b/experiments/02_term_expansion_by_language_pair/report/dev_v1_proper_term_across_languages.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
     <font>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +64,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -165,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -183,6 +192,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1425,9 +1437,9 @@
       <c r="Q11" s="7" t="n">
         <v>0.9720018885741264</v>
       </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>ende</t>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>tie</t>
         </is>
       </c>
       <c r="S11" s="7" t="n">
